--- a/fichier_config_PIF.xlsx
+++ b/fichier_config_PIF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demanet\Documents\pifprevis-main - TEST - CNT2AC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demanet\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F937A5-7AD2-491A-9CC8-6220363F772B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943A4AC7-B1D5-4825-B635-A643C728E86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-16380" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{1E9F1C0A-3D2F-4596-8E04-B8791B8B0FB9}"/>
+    <workbookView xWindow="-25740" yWindow="-14130" windowWidth="21660" windowHeight="11295" xr2:uid="{1E9F1C0A-3D2F-4596-8E04-B8791B8B0FB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="2" r:id="rId1"/>
@@ -1357,7 +1357,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950742B2-FA79-431D-B1B2-E7A47C082980}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1393,17 +1393,15 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
       <c r="B5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
         <v>50</v>
       </c>
     </row>
